--- a/artfynd/A 61488-2025 artfynd.xlsx
+++ b/artfynd/A 61488-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135743015</v>
       </c>
       <c r="B2" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135743018</v>
       </c>
       <c r="B3" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135743019</v>
       </c>
       <c r="B4" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135743021</v>
       </c>
       <c r="B5" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135743022</v>
       </c>
       <c r="B6" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135743024</v>
       </c>
       <c r="B7" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135743025</v>
       </c>
       <c r="B8" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135743026</v>
       </c>
       <c r="B9" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135743027</v>
       </c>
       <c r="B10" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135743017</v>
       </c>
       <c r="B11" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135743020</v>
       </c>
       <c r="B12" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 61488-2025 artfynd.xlsx
+++ b/artfynd/A 61488-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135743015</v>
       </c>
       <c r="B2" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135743018</v>
       </c>
       <c r="B3" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135743019</v>
       </c>
       <c r="B4" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135743021</v>
       </c>
       <c r="B5" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135743022</v>
       </c>
       <c r="B6" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135743024</v>
       </c>
       <c r="B7" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135743025</v>
       </c>
       <c r="B8" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135743026</v>
       </c>
       <c r="B9" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135743027</v>
       </c>
       <c r="B10" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135743017</v>
       </c>
       <c r="B11" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135743020</v>
       </c>
       <c r="B12" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 61488-2025 artfynd.xlsx
+++ b/artfynd/A 61488-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135743015</v>
       </c>
       <c r="B2" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135743018</v>
       </c>
       <c r="B3" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135743019</v>
       </c>
       <c r="B4" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135743021</v>
       </c>
       <c r="B5" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135743022</v>
       </c>
       <c r="B6" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135743024</v>
       </c>
       <c r="B7" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135743025</v>
       </c>
       <c r="B8" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135743026</v>
       </c>
       <c r="B9" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135743027</v>
       </c>
       <c r="B10" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135743017</v>
       </c>
       <c r="B11" t="n">
-        <v>83431</v>
+        <v>83432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135743020</v>
       </c>
       <c r="B12" t="n">
-        <v>83431</v>
+        <v>83432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 61488-2025 artfynd.xlsx
+++ b/artfynd/A 61488-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135743015</v>
       </c>
       <c r="B2" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135743018</v>
       </c>
       <c r="B3" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135743019</v>
       </c>
       <c r="B4" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135743021</v>
       </c>
       <c r="B5" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135743022</v>
       </c>
       <c r="B6" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135743024</v>
       </c>
       <c r="B7" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135743025</v>
       </c>
       <c r="B8" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135743026</v>
       </c>
       <c r="B9" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135743027</v>
       </c>
       <c r="B10" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135743017</v>
       </c>
       <c r="B11" t="n">
-        <v>83432</v>
+        <v>83436</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135743020</v>
       </c>
       <c r="B12" t="n">
-        <v>83432</v>
+        <v>83436</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 61488-2025 artfynd.xlsx
+++ b/artfynd/A 61488-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135743015</v>
       </c>
       <c r="B2" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135743018</v>
       </c>
       <c r="B3" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135743019</v>
       </c>
       <c r="B4" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135743021</v>
       </c>
       <c r="B5" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135743022</v>
       </c>
       <c r="B6" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135743024</v>
       </c>
       <c r="B7" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135743025</v>
       </c>
       <c r="B8" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135743026</v>
       </c>
       <c r="B9" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135743027</v>
       </c>
       <c r="B10" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135743017</v>
       </c>
       <c r="B11" t="n">
-        <v>83436</v>
+        <v>83437</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135743020</v>
       </c>
       <c r="B12" t="n">
-        <v>83436</v>
+        <v>83437</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 61488-2025 artfynd.xlsx
+++ b/artfynd/A 61488-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135743015</v>
       </c>
       <c r="B2" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135743018</v>
       </c>
       <c r="B3" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135743019</v>
       </c>
       <c r="B4" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135743021</v>
       </c>
       <c r="B5" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135743022</v>
       </c>
       <c r="B6" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135743024</v>
       </c>
       <c r="B7" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135743025</v>
       </c>
       <c r="B8" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135743026</v>
       </c>
       <c r="B9" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135743027</v>
       </c>
       <c r="B10" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135743017</v>
       </c>
       <c r="B11" t="n">
-        <v>83437</v>
+        <v>83441</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135743020</v>
       </c>
       <c r="B12" t="n">
-        <v>83437</v>
+        <v>83441</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 61488-2025 artfynd.xlsx
+++ b/artfynd/A 61488-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135743015</v>
       </c>
       <c r="B2" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135743018</v>
       </c>
       <c r="B3" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135743019</v>
       </c>
       <c r="B4" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135743021</v>
       </c>
       <c r="B5" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135743022</v>
       </c>
       <c r="B6" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135743024</v>
       </c>
       <c r="B7" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135743025</v>
       </c>
       <c r="B8" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135743026</v>
       </c>
       <c r="B9" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135743027</v>
       </c>
       <c r="B10" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135743017</v>
       </c>
       <c r="B11" t="n">
-        <v>83441</v>
+        <v>83447</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135743020</v>
       </c>
       <c r="B12" t="n">
-        <v>83441</v>
+        <v>83447</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
